--- a/docs/MV-AutoML-Studio-Analisis.xlsx
+++ b/docs/MV-AutoML-Studio-Analisis.xlsx
@@ -1048,7 +1048,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Sin firma digital, sin actualización automática dentro del programa y sin versión para macOS ni Linux. El instalador pesa alrededor de 1,6 GB por las bibliotecas de ML.</t>
+          <t>Sin firma digital, sin actualización automática dentro del programa y sin versión para macOS ni Linux. El instalador pesa 375 MB y ocupa cerca de 1,6 GB una vez instalado, por las bibliotecas de ML.</t>
         </is>
       </c>
     </row>

--- a/docs/MV-AutoML-Studio-Analisis.xlsx
+++ b/docs/MV-AutoML-Studio-Analisis.xlsx
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>El instalador no está firmado digitalmente: Windows SmartScreen va a mostrar una advertencia hasta juntar reputación (un certificado EV cuesta entre US$ 250 y 400 al año). Falta límite de intentos en las funciones del sitio, y el panel se protege con una sola contraseña sin segundo factor. El repositorio todavía es público.</t>
+          <t>El instalador no está firmado digitalmente: Windows SmartScreen va a mostrar una advertencia hasta juntar reputación (un certificado EV cuesta entre US$ 250 y 400 al año). Falta límite de intentos en las funciones del sitio, y el panel se protege con una sola contraseña sin segundo factor. El repositorio todavía es público, aunque el instalador ya no.</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Instalador NSIS asistido: el usuario elige el disco y la carpeta, no se clava en C:. Crea acceso directo en Escritorio y Menú de inicio, deja desinstalador registrado, e instala por usuario sin pedir permisos de administrador. Se compila solo en cada integración y publica dos versiones: demo pública y owner en borrador privado.</t>
+          <t>Instalador NSIS asistido: el usuario elige el disco y la carpeta, no se clava en C:. Crea acceso directo en Escritorio y Menú de inicio, deja desinstalador registrado, e instala por usuario sin pedir permisos de administrador. Se compila solo en cada integración y publica dos versiones, las dos en releases privados: la del cliente, que entrega el sitio sólo contra una licencia válida, y la de dueño.</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1079,16 +1079,16 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Sitio en tres idiomas con video narrado por idioma, precios claros, cobro con MercadoPago del lado del servidor, página de gracias y descarga directa del instalador. Todo estático: carga rápido y no cuesta nada mantenerlo.</t>
+          <t>Sitio en tres idiomas con video narrado por idioma, precios claros, cobro con MercadoPago del lado del servidor y formulario de pedido de demo que llega por correo. El instalador no se regala: se muestra en vivo y se entrega contra licencia, así que cada interesado deja nombre, empresa y correo en vez de bajar el producto y desaparecer. Todo estático: carga rápido y no cuesta nada mantenerlo.</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>No hay dominio propio, ni prueba social (casos, logos, testimonios), ni contenido para buscadores, ni medición de visitas. Sin eso el sitio convierte a quien ya venía decidido, no capta.</t>
+          <t>No hay dominio propio, ni prueba social (casos, logos, testimonios), ni contenido para buscadores, ni medición de visitas. Y el pedido de demo agrega fricción: convierte menos visitantes en pruebas, a cambio de que las pruebas valgan más. Hay que mirar cuántos pedidos entran por mes antes de dar por buena esa apuesta.</t>
         </is>
       </c>
     </row>
